--- a/artfynd/A 52190-2020 artfynd.xlsx
+++ b/artfynd/A 52190-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52190-2020 artfynd.xlsx
+++ b/artfynd/A 52190-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1029,6 +1029,332 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127760438</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98471</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Älgen/Skrållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>385772</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6973477</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Suvi Sivula</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Suvi Sivula, Jan  Olsson, Magnus Svensson, Maria Ahlefelt, Ola Elleström, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127760836</v>
+      </c>
+      <c r="B6" t="n">
+        <v>75144</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skrållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>385790</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6973457</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Magnus Svensson</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Strid, Jan  Olsson, Stefan Phalagorn Bergström, Suvi Sivula, Ola Elleström, Magnus Svensson, Maria Ahlefelt, Eva Grönlund, Åsa Kruys</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127759986</v>
+      </c>
+      <c r="B7" t="n">
+        <v>82861</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skrållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>385849</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6973444</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Strid, Jan  Olsson, Stefan Phalagorn Bergström, Suvi Sivula, Ola Elleström, Magnus Svensson, Maria Ahlefelt, Eva Grönlund, Åsa Kruys</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Sveriges Mykologiska Förenings kursverksamhet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52190-2020 artfynd.xlsx
+++ b/artfynd/A 52190-2020 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>127760438</v>
       </c>
       <c r="B5" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Strid, Jan  Olsson, Stefan Phalagorn Bergström, Suvi Sivula, Ola Elleström, Magnus Svensson, Maria Ahlefelt, Eva Grönlund, Åsa Kruys</t>
+          <t>Thomas Strid, Ola Elleström, Suvi Sivula, Stefan Phalagorn Bergström, Jan  Olsson, Åsa Kruys, Eva Grönlund, Maria Ahlefelt, Magnus Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 52190-2020 artfynd.xlsx
+++ b/artfynd/A 52190-2020 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>127760438</v>
       </c>
       <c r="B5" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>127760836</v>
       </c>
       <c r="B6" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>127759986</v>
       </c>
       <c r="B7" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Strid, Ola Elleström, Suvi Sivula, Stefan Phalagorn Bergström, Jan  Olsson, Åsa Kruys, Eva Grönlund, Maria Ahlefelt, Magnus Svensson</t>
+          <t>Thomas Strid, Jan  Olsson, Stefan Phalagorn Bergström, Suvi Sivula, Ola Elleström, Magnus Svensson, Maria Ahlefelt, Eva Grönlund, Åsa Kruys</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 52190-2020 artfynd.xlsx
+++ b/artfynd/A 52190-2020 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>127760438</v>
       </c>
       <c r="B5" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Jan  Olsson, Magnus Svensson, Maria Ahlefelt, Ola Elleström, Stefan Phalagorn Bergström</t>
+          <t>Stefan Phalagorn Bergström, Ola Elleström, Maria Ahlefelt, Magnus Svensson, Jan  Olsson, Suvi Sivula</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1141,7 +1141,7 @@
         <v>127760836</v>
       </c>
       <c r="B6" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>127759986</v>
       </c>
       <c r="B7" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52190-2020 artfynd.xlsx
+++ b/artfynd/A 52190-2020 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>127760438</v>
       </c>
       <c r="B5" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Phalagorn Bergström, Ola Elleström, Maria Ahlefelt, Magnus Svensson, Jan  Olsson, Suvi Sivula</t>
+          <t>Suvi Sivula, Jan  Olsson, Magnus Svensson, Maria Ahlefelt, Ola Elleström, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 52190-2020 artfynd.xlsx
+++ b/artfynd/A 52190-2020 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>127760438</v>
       </c>
       <c r="B5" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52190-2020 artfynd.xlsx
+++ b/artfynd/A 52190-2020 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>127760438</v>
       </c>
       <c r="B5" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52190-2020 artfynd.xlsx
+++ b/artfynd/A 52190-2020 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>127760438</v>
       </c>
       <c r="B5" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>127760836</v>
       </c>
       <c r="B6" t="n">
-        <v>75153</v>
+        <v>75156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>127759986</v>
       </c>
       <c r="B7" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52190-2020 artfynd.xlsx
+++ b/artfynd/A 52190-2020 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>127760438</v>
       </c>
       <c r="B5" t="n">
-        <v>98499</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>127760836</v>
       </c>
       <c r="B6" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>127759986</v>
       </c>
       <c r="B7" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
